--- a/data/Drop Master with final correct options.xlsx
+++ b/data/Drop Master with final correct options.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mckinsey-my.sharepoint.com/personal/vinod_krishnan_external_mckinsey_com/Documents/Desktop/rpl6-predictor-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{36F9443B-6CC9-4D70-8A98-A235CCD13019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{048B2D57-0871-4896-BDA1-17E26AFAA833}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{36F9443B-6CC9-4D70-8A98-A235CCD13019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{585AB6EC-4679-4059-9C57-73BEFD5DE929}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0ADF93B2-9E8A-484E-A59A-338300554658}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="103">
   <si>
     <t>Drop #</t>
   </si>
@@ -239,9 +239,6 @@
     <t>Actuals in RPL 6</t>
   </si>
   <si>
-    <t xml:space="preserve">Nobody scored a century. Highest score was 69. </t>
-  </si>
-  <si>
     <t>Sheikh was bought by Strikers</t>
   </si>
   <si>
@@ -254,16 +251,10 @@
     <t>119 was the average 1st innings score</t>
   </si>
   <si>
-    <t>Warriors were all out for 75 in their match vs Warriors</t>
-  </si>
-  <si>
     <t>These 8 were run out during RPL 6: MVP, Sridhar, Nattu, Mani, Arvind, Sreejith, Anush, Ram</t>
   </si>
   <si>
     <t>Strikers were all out against Warriors as well as Super Kings. Warriors were all out against Super Kings in the finals</t>
-  </si>
-  <si>
-    <t>Arun scored 69 against Strikers in the first match of RPL 6</t>
   </si>
   <si>
     <t>Match 1: penalty for Strikers
@@ -272,9 +263,6 @@
 Match 7: penalty for Warriors</t>
   </si>
   <si>
-    <t>Arun came in to bat at #6 in match 1 when he scored 69 vs Strikers</t>
-  </si>
-  <si>
     <t>Warriors won all their leagues matches vs the other 3 teams</t>
   </si>
   <si>
@@ -317,41 +305,56 @@
     <t>Super Kings made 124-11 and defended the score in the finals vs Warriors</t>
   </si>
   <si>
-    <t>Deepak won 3 tosses in RPL 6. he lost the toss only to Mani during the their match vs Strikers</t>
-  </si>
-  <si>
     <t>Arun had the best batting average of 32.3 in RPL 6</t>
   </si>
   <si>
-    <t>Sreejith, Anush and Ram were run out on the finals</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>Karthic R gave only 0 runs in his 3 overs in the finals vs Warriors</t>
+    <t>None. The highest scroe was 159 in RPL 6.</t>
+  </si>
+  <si>
+    <t>33 in 3 overs were conceded by Sai (vs Super Kings), Krishnan (vs Warriors) and MVP (vs Rockstars)</t>
+  </si>
+  <si>
+    <t>You know your answer :)</t>
+  </si>
+  <si>
+    <t>Sanjay was man of the match twice. Once against Rockstars and then against Strikers.</t>
+  </si>
+  <si>
+    <t>There were no successful DRS reviews taken in RPL 6 - highlighting the brilliant umpiring standards in the tournament. Hats off to all the umpires for not only calling it right, but also bearing the heat to ensure we have an error free RPL 6!!</t>
+  </si>
+  <si>
+    <t>Nobody scored a century. Highest score was 67</t>
+  </si>
+  <si>
+    <t>Warriors were all out for 75 in their match vs Super Kings</t>
+  </si>
+  <si>
+    <t>Arun scored 67 against Strikers in the first match of RPL 6</t>
+  </si>
+  <si>
+    <t>Arun came in to bat at #6 in match 1 when he scored 67 vs Strikers</t>
+  </si>
+  <si>
+    <t>There was a technical flaw in the options given for this question. Hence, the drop was scrapped!</t>
+  </si>
+  <si>
+    <t>Deepak won 3 tosses in RPL 6. He lost the toss only to Mani during the their match vs Strikers</t>
+  </si>
+  <si>
+    <t>Sreejith, Anush and Ram were run out in the finals</t>
+  </si>
+  <si>
+    <t>No such instances occurred during RPL 6</t>
+  </si>
+  <si>
+    <t>Karthic R gave only 0 runs in his 3 overs in the finals vs Warriors [excluding extras]</t>
   </si>
   <si>
     <t>These 4 bowlers took c&amp;b wickets:
-- Shyam (Karthic R)
-- Naren (Yogi)
-- Arun Aero (Vignesh)
-- Ranga (Shyam)</t>
-  </si>
-  <si>
-    <t>None. The highest scroe was 159 in RPL 6.</t>
-  </si>
-  <si>
-    <t>33 in 3 overs were conceded by Sai (vs Super Kings), Krishnan (vs Warriors) and MVP (vs Rockstars)</t>
-  </si>
-  <si>
-    <t>You know your answer :)</t>
-  </si>
-  <si>
-    <t>Sanjay was man of the match twice. Once against Rockstars and then against Strikers.</t>
-  </si>
-  <si>
-    <t>There were no successful DRS reviews taken in RPL 6 - highlighting the brilliant umpiring standards in the tournament. Hats off to all the umpires for not only calling it right, but also bearing the heat to ensure we have an error free RPL 6!!</t>
+- Shyam (dismissed Karthic R)
+- Naren (dismissed Yogi)
+- Arun Aero (dismissed Vignesh)
+- Ranga (dismissed Shyam)</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1038,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -1049,7 +1052,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -1063,7 +1066,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -1077,7 +1080,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="2:5">
@@ -1091,7 +1094,7 @@
         <v>9</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="2:5">
@@ -1105,10 +1108,10 @@
         <v>11</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" ht="26.4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
       <c r="B9" s="3">
         <v>7</v>
       </c>
@@ -1119,10 +1122,10 @@
         <v>13</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" ht="39.6">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="26.4">
       <c r="B10" s="6">
         <v>8</v>
       </c>
@@ -1133,7 +1136,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -1147,10 +1150,10 @@
         <v>1</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" ht="66">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="52.8">
       <c r="B12" s="6">
         <v>10</v>
       </c>
@@ -1161,10 +1164,10 @@
         <v>17</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" ht="26.4">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5">
       <c r="B13" s="3">
         <v>11</v>
       </c>
@@ -1175,7 +1178,7 @@
         <v>13</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="2:5">
@@ -1188,7 +1191,9 @@
       <c r="D14" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="8"/>
+      <c r="E14" s="8" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="3">
@@ -1201,7 +1206,7 @@
         <v>22</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="2:5" ht="52.8">
@@ -1215,7 +1220,7 @@
         <v>24</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="2:5">
@@ -1229,10 +1234,10 @@
         <v>26</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" ht="26.4">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
       <c r="B18" s="6">
         <v>16</v>
       </c>
@@ -1243,7 +1248,7 @@
         <v>28</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="2:5">
@@ -1257,7 +1262,7 @@
         <v>30</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="2:5">
@@ -1271,7 +1276,7 @@
         <v>32</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="2:5">
@@ -1285,7 +1290,7 @@
         <v>34</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="2:5">
@@ -1299,7 +1304,7 @@
         <v>36</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="26.4">
@@ -1313,7 +1318,7 @@
         <v>38</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="2:5">
@@ -1327,7 +1332,7 @@
         <v>4</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="2:5">
@@ -1341,10 +1346,10 @@
         <v>41</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" ht="52.8">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="26.4">
       <c r="B26" s="19">
         <v>24</v>
       </c>
@@ -1355,10 +1360,10 @@
         <v>43</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" ht="26.4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
       <c r="B27" s="18">
         <v>25</v>
       </c>
@@ -1369,10 +1374,10 @@
         <v>45</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" ht="26.4">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
       <c r="B28" s="19">
         <v>26</v>
       </c>
@@ -1383,7 +1388,7 @@
         <v>22</v>
       </c>
       <c r="E28" s="29" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="2:5">
@@ -1397,7 +1402,7 @@
         <v>48</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="2:5">
@@ -1411,7 +1416,7 @@
         <v>3</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="2:5">
@@ -1425,10 +1430,10 @@
         <v>0</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" ht="26.4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5">
       <c r="B32" s="19">
         <v>30</v>
       </c>
@@ -1439,7 +1444,7 @@
         <v>52</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="2:5" ht="66">
@@ -1453,7 +1458,7 @@
         <v>54</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="2:5">
@@ -1467,10 +1472,10 @@
         <v>56</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" ht="26.4">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5">
       <c r="B35" s="18">
         <v>33</v>
       </c>
@@ -1481,7 +1486,7 @@
         <v>58</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="2:5">
@@ -1495,7 +1500,7 @@
         <v>60</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="2:5">
@@ -1509,7 +1514,7 @@
         <v>60</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="2:5">
@@ -1523,10 +1528,10 @@
         <v>60</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" ht="26.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5">
       <c r="B39" s="18">
         <v>37</v>
       </c>
@@ -1537,10 +1542,10 @@
         <v>22</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" ht="66">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" ht="39.6">
       <c r="B40" s="19">
         <v>38</v>
       </c>
@@ -1551,7 +1556,7 @@
         <v>65</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
